--- a/launch/rs/design/booth/megashow/megashow_KDRS_rental_form.xlsx
+++ b/launch/rs/design/booth/megashow/megashow_KDRS_rental_form.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="application form" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'비품임대신청서'!$A$1:$Q$40</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'비품임대신청서'!$A$1:$Q$38</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'application form'!$A$1:$H$35</definedName>
   </definedNames>
   <calcPr calcId="144525" fullCalcOnLoad="1" concurrentCalc="0"/>
@@ -1483,7 +1483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q40"/>
+  <dimension ref="A1:Q38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
     <col width="5.875" customWidth="1" style="1" min="1" max="1"/>
@@ -1764,20 +1764,20 @@
       </c>
       <c r="B10" s="100" t="inlineStr">
         <is>
-          <t>3단진열대</t>
+          <t>3단쇼케이스진열대(냉장냉동X)</t>
         </is>
       </c>
       <c r="C10" s="101" t="n"/>
       <c r="D10" s="102" t="inlineStr">
         <is>
-          <t>W1480×900×1000</t>
+          <t>W900×450×900</t>
         </is>
       </c>
       <c r="E10" s="103" t="n">
         <v>1</v>
       </c>
       <c r="F10" s="104" t="n">
-        <v>110000</v>
+        <v>70000</v>
       </c>
       <c r="G10" s="105">
         <f>E10*F10</f>
@@ -1785,7 +1785,7 @@
       </c>
       <c r="H10" s="106" t="inlineStr">
         <is>
-          <t>워킹화</t>
+          <t>구강용품</t>
         </is>
       </c>
       <c r="I10" s="31" t="n"/>
@@ -1796,20 +1796,20 @@
       </c>
       <c r="B11" s="107" t="inlineStr">
         <is>
-          <t>2단진열대</t>
+          <t>1단쇼케이스진열대(냉장냉동X)</t>
         </is>
       </c>
       <c r="C11" s="101" t="n"/>
       <c r="D11" s="108" t="inlineStr">
         <is>
-          <t>W1480×600×1000</t>
+          <t>W900×450×900</t>
         </is>
       </c>
       <c r="E11" s="103" t="n">
         <v>1</v>
       </c>
       <c r="F11" s="104" t="n">
-        <v>80000</v>
+        <v>60000</v>
       </c>
       <c r="G11" s="105">
         <f>E11*F11</f>
@@ -1817,7 +1817,7 @@
       </c>
       <c r="H11" s="106" t="inlineStr">
         <is>
-          <t>인솔 체험</t>
+          <t>자문 코너</t>
         </is>
       </c>
       <c r="I11" s="31" t="n"/>
@@ -1828,20 +1828,20 @@
       </c>
       <c r="B12" s="107" t="inlineStr">
         <is>
-          <t>땅콩의자(검정)</t>
+          <t>1단진열대</t>
         </is>
       </c>
       <c r="C12" s="101" t="n"/>
       <c r="D12" s="108" t="inlineStr">
         <is>
-          <t>W450×580×450</t>
+          <t>W1480×600×750</t>
         </is>
       </c>
       <c r="E12" s="103" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F12" s="104" t="n">
-        <v>20000</v>
+        <v>60000</v>
       </c>
       <c r="G12" s="105">
         <f>E12*F12</f>
@@ -1849,7 +1849,7 @@
       </c>
       <c r="H12" s="106" t="inlineStr">
         <is>
-          <t>시착 3 · 상담 1</t>
+          <t>앞선 카운터(커버 자체)</t>
         </is>
       </c>
       <c r="I12" s="31" t="n"/>
@@ -1860,20 +1860,20 @@
       </c>
       <c r="B13" s="100" t="inlineStr">
         <is>
-          <t>전신거울</t>
+          <t>땅콩의자(검정)</t>
         </is>
       </c>
       <c r="C13" s="101" t="n"/>
       <c r="D13" s="102" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>W450×580×450</t>
         </is>
       </c>
       <c r="E13" s="103" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F13" s="104" t="n">
-        <v>30000</v>
+        <v>20000</v>
       </c>
       <c r="G13" s="105">
         <f>E13*F13</f>
@@ -1881,7 +1881,7 @@
       </c>
       <c r="H13" s="106" t="inlineStr">
         <is>
-          <t>시착</t>
+          <t>시착 3 · 상담 1</t>
         </is>
       </c>
       <c r="I13" s="31" t="n"/>
@@ -1892,7 +1892,7 @@
       </c>
       <c r="B14" s="107" t="inlineStr">
         <is>
-          <t>TV 50"</t>
+          <t>전신거울</t>
         </is>
       </c>
       <c r="C14" s="101" t="n"/>
@@ -1905,7 +1905,7 @@
         <v>1</v>
       </c>
       <c r="F14" s="104" t="n">
-        <v>350000</v>
+        <v>30000</v>
       </c>
       <c r="G14" s="105">
         <f>E14*F14</f>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="H14" s="109" t="inlineStr">
         <is>
-          <t>영상 USB 재생</t>
+          <t>시착</t>
         </is>
       </c>
       <c r="I14" s="31" t="n"/>
@@ -1924,20 +1924,20 @@
       </c>
       <c r="B15" s="100" t="inlineStr">
         <is>
-          <t>1단쇼케이스진열대(냉장냉동X)</t>
+          <t>TV 50"</t>
         </is>
       </c>
       <c r="C15" s="101" t="n"/>
       <c r="D15" s="102" t="inlineStr">
         <is>
-          <t>W900×450×900</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E15" s="103" t="n">
         <v>1</v>
       </c>
       <c r="F15" s="104" t="n">
-        <v>60000</v>
+        <v>350000</v>
       </c>
       <c r="G15" s="105">
         <f>E15*F15</f>
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H15" s="106" t="inlineStr">
         <is>
-          <t>자문 코너</t>
+          <t>영상 USB 재생</t>
         </is>
       </c>
       <c r="I15" s="31" t="n"/>
@@ -1956,20 +1956,20 @@
       </c>
       <c r="B16" s="100" t="inlineStr">
         <is>
-          <t>3단쇼케이스진열대(냉장냉동X)</t>
+          <t>선반진열대(옥타부스용)</t>
         </is>
       </c>
       <c r="C16" s="101" t="n"/>
       <c r="D16" s="102" t="inlineStr">
         <is>
-          <t>W900×450×900</t>
+          <t>W1000×300</t>
         </is>
       </c>
       <c r="E16" s="103" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F16" s="104" t="n">
-        <v>70000</v>
+        <v>30000</v>
       </c>
       <c r="G16" s="105">
         <f>E16*F16</f>
@@ -1977,7 +1977,7 @@
       </c>
       <c r="H16" s="106" t="inlineStr">
         <is>
-          <t>구강용품</t>
+          <t>우측벽 판넬 각 1</t>
         </is>
       </c>
       <c r="I16" s="31" t="n"/>
@@ -1988,20 +1988,20 @@
       </c>
       <c r="B17" s="100" t="inlineStr">
         <is>
-          <t>1단진열대</t>
+          <t>스탠드 카달로그 꽂이</t>
         </is>
       </c>
       <c r="C17" s="101" t="n"/>
       <c r="D17" s="102" t="inlineStr">
         <is>
-          <t>W1480×600×750</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E17" s="103" t="n">
         <v>1</v>
       </c>
       <c r="F17" s="104" t="n">
-        <v>60000</v>
+        <v>30000</v>
       </c>
       <c r="G17" s="105">
         <f>E17*F17</f>
@@ -2009,7 +2009,7 @@
       </c>
       <c r="H17" s="106" t="inlineStr">
         <is>
-          <t>욕실화</t>
+          <t>리플렛</t>
         </is>
       </c>
       <c r="I17" s="31" t="n"/>
@@ -2020,20 +2020,20 @@
       </c>
       <c r="B18" s="100" t="inlineStr">
         <is>
-          <t>선반진열대(옥타부스용)</t>
+          <t>POP스텐드</t>
         </is>
       </c>
       <c r="C18" s="101" t="n"/>
       <c r="D18" s="102" t="inlineStr">
         <is>
-          <t>W1000×300</t>
+          <t>W350×H1200~2000</t>
         </is>
       </c>
       <c r="E18" s="103" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F18" s="104" t="n">
-        <v>30000</v>
+        <v>20000</v>
       </c>
       <c r="G18" s="105">
         <f>E18*F18</f>
@@ -2041,7 +2041,7 @@
       </c>
       <c r="H18" s="110" t="inlineStr">
         <is>
-          <t>우측벽 판넬 각 1</t>
+          <t>POP</t>
         </is>
       </c>
       <c r="I18" s="31" t="n"/>
@@ -2052,20 +2052,20 @@
       </c>
       <c r="B19" s="100" t="inlineStr">
         <is>
-          <t>스탠드 카달로그 꽂이</t>
+          <t>행운함</t>
         </is>
       </c>
       <c r="C19" s="101" t="n"/>
       <c r="D19" s="102" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>W350×350×350</t>
         </is>
       </c>
       <c r="E19" s="103" t="n">
         <v>1</v>
       </c>
       <c r="F19" s="104" t="n">
-        <v>30000</v>
+        <v>25000</v>
       </c>
       <c r="G19" s="105">
         <f>E19*F19</f>
@@ -2073,7 +2073,7 @@
       </c>
       <c r="H19" s="110" t="inlineStr">
         <is>
-          <t>리플렛</t>
+          <t>명함 응모함</t>
         </is>
       </c>
     </row>
@@ -2083,178 +2083,132 @@
       </c>
       <c r="B20" s="100" t="inlineStr">
         <is>
-          <t>POP스텐드</t>
+          <t>휴지통</t>
         </is>
       </c>
       <c r="C20" s="101" t="n"/>
       <c r="D20" s="102" t="inlineStr">
         <is>
-          <t>W350×1200~2000</t>
+          <t>50L</t>
         </is>
       </c>
       <c r="E20" s="103" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F20" s="104" t="n">
-        <v>20000</v>
+        <v>5000</v>
       </c>
       <c r="G20" s="105">
         <f>E20*F20</f>
         <v/>
       </c>
-      <c r="H20" s="110" t="inlineStr">
-        <is>
-          <t>POP</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="21.75" customHeight="1" s="88" thickBot="1">
-      <c r="A21" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="B21" s="100" t="inlineStr">
-        <is>
-          <t>행운함</t>
-        </is>
-      </c>
-      <c r="C21" s="101" t="n"/>
-      <c r="D21" s="102" t="inlineStr">
-        <is>
-          <t>W350×350×350</t>
-        </is>
-      </c>
-      <c r="E21" s="103" t="n">
-        <v>1</v>
-      </c>
-      <c r="F21" s="104" t="n">
-        <v>25000</v>
-      </c>
-      <c r="G21" s="105">
-        <f>E21*F21</f>
+      <c r="H20" s="110" t="inlineStr"/>
+    </row>
+    <row r="21" ht="18.75" customHeight="1" s="88" thickBot="1">
+      <c r="A21" s="44" t="inlineStr">
+        <is>
+          <t>계 ㅣ Total</t>
+        </is>
+      </c>
+      <c r="B21" s="111" t="n"/>
+      <c r="C21" s="111" t="n"/>
+      <c r="D21" s="111" t="n"/>
+      <c r="E21" s="111" t="n"/>
+      <c r="F21" s="112">
+        <f>SUM(G9:G20)</f>
         <v/>
       </c>
-      <c r="H21" s="110" t="inlineStr">
-        <is>
-          <t>명함 응모함</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="21.75" customHeight="1" s="88">
-      <c r="A22" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="B22" s="100" t="inlineStr">
-        <is>
-          <t>휴지통</t>
-        </is>
-      </c>
-      <c r="C22" s="101" t="n"/>
-      <c r="D22" s="102" t="inlineStr">
-        <is>
-          <t>50L</t>
-        </is>
-      </c>
-      <c r="E22" s="103" t="n">
-        <v>1</v>
-      </c>
-      <c r="F22" s="104" t="n">
-        <v>5000</v>
-      </c>
-      <c r="G22" s="105">
-        <f>E22*F22</f>
+      <c r="G21" s="111" t="n"/>
+      <c r="H21" s="113" t="n"/>
+      <c r="I21" s="34" t="n"/>
+    </row>
+    <row r="22" ht="18.75" customHeight="1" s="88">
+      <c r="A22" s="47" t="inlineStr">
+        <is>
+          <t>V.A.T</t>
+        </is>
+      </c>
+      <c r="B22" s="114" t="n"/>
+      <c r="C22" s="114" t="n"/>
+      <c r="D22" s="114" t="n"/>
+      <c r="E22" s="114" t="n"/>
+      <c r="F22" s="115">
+        <f>ROUND(F21*0.1,0)</f>
         <v/>
       </c>
-      <c r="H22" s="110" t="inlineStr"/>
+      <c r="G22" s="114" t="n"/>
+      <c r="H22" s="116" t="n"/>
+      <c r="I22" s="34" t="n"/>
     </row>
     <row r="23" ht="18.75" customHeight="1" s="88">
-      <c r="A23" s="44" t="inlineStr">
-        <is>
-          <t>계 ㅣ Total</t>
-        </is>
-      </c>
-      <c r="B23" s="111" t="n"/>
-      <c r="C23" s="111" t="n"/>
-      <c r="D23" s="111" t="n"/>
-      <c r="E23" s="111" t="n"/>
-      <c r="F23" s="112">
-        <f>SUM(G9:G22)</f>
+      <c r="A23" s="41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   총   계 ㅣ Grand Total</t>
+        </is>
+      </c>
+      <c r="B23" s="117" t="n"/>
+      <c r="C23" s="117" t="n"/>
+      <c r="D23" s="117" t="n"/>
+      <c r="E23" s="117" t="n"/>
+      <c r="F23" s="118">
+        <f>F21+F22</f>
         <v/>
       </c>
-      <c r="G23" s="111" t="n"/>
-      <c r="H23" s="113" t="n"/>
+      <c r="G23" s="117" t="n"/>
+      <c r="H23" s="119" t="n"/>
       <c r="I23" s="34" t="n"/>
     </row>
-    <row r="24" ht="18.75" customHeight="1" s="88">
-      <c r="A24" s="47" t="inlineStr">
-        <is>
-          <t>V.A.T</t>
-        </is>
-      </c>
-      <c r="B24" s="114" t="n"/>
-      <c r="C24" s="114" t="n"/>
-      <c r="D24" s="114" t="n"/>
-      <c r="E24" s="114" t="n"/>
-      <c r="F24" s="115">
-        <f>ROUND(F23*0.1,0)</f>
-        <v/>
-      </c>
-      <c r="G24" s="114" t="n"/>
-      <c r="H24" s="116" t="n"/>
-      <c r="I24" s="34" t="n"/>
-    </row>
-    <row r="25" ht="18.75" customHeight="1" s="88">
-      <c r="A25" s="41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   총   계 ㅣ Grand Total</t>
-        </is>
-      </c>
-      <c r="B25" s="117" t="n"/>
-      <c r="C25" s="117" t="n"/>
-      <c r="D25" s="117" t="n"/>
-      <c r="E25" s="117" t="n"/>
-      <c r="F25" s="118">
-        <f>F23+F24</f>
-        <v/>
-      </c>
-      <c r="G25" s="117" t="n"/>
-      <c r="H25" s="119" t="n"/>
-      <c r="I25" s="34" t="n"/>
-    </row>
-    <row r="26" ht="24" customHeight="1" s="88">
-      <c r="A26" s="69" t="inlineStr">
+    <row r="24" ht="24" customHeight="1" s="88">
+      <c r="A24" s="69" t="inlineStr">
         <is>
           <t>위와 같이 신청합니다.</t>
         </is>
       </c>
-      <c r="I26" s="84" t="n"/>
+      <c r="I24" s="84" t="n"/>
+    </row>
+    <row r="25" s="88">
+      <c r="A25" s="71" t="inlineStr">
+        <is>
+          <t>■은행송금시 입금계좌 :</t>
+        </is>
+      </c>
+      <c r="D25" s="71" t="inlineStr">
+        <is>
+          <t>NH농협은행</t>
+        </is>
+      </c>
+      <c r="E25" s="71" t="inlineStr">
+        <is>
+          <t>301-0194-1261-21</t>
+        </is>
+      </c>
+      <c r="G25" s="71" t="inlineStr">
+        <is>
+          <t>예금주: ㈜케이디알에스</t>
+        </is>
+      </c>
+      <c r="I25" s="72" t="n"/>
+    </row>
+    <row r="26" s="88">
+      <c r="A26" s="71" t="inlineStr">
+        <is>
+          <t>■결제방법을 체크해 주세요.</t>
+        </is>
+      </c>
+      <c r="I26" s="72" t="n"/>
     </row>
     <row r="27" s="88">
-      <c r="A27" s="71" t="inlineStr">
-        <is>
-          <t>■은행송금시 입금계좌 :</t>
-        </is>
-      </c>
-      <c r="D27" s="71" t="inlineStr">
-        <is>
-          <t>NH농협은행</t>
-        </is>
-      </c>
-      <c r="E27" s="71" t="inlineStr">
-        <is>
-          <t>301-0194-1261-21</t>
-        </is>
-      </c>
-      <c r="G27" s="71" t="inlineStr">
-        <is>
-          <t>예금주: ㈜케이디알에스</t>
+      <c r="A27" s="72" t="inlineStr">
+        <is>
+          <t>□은행송금             □현장현금결제             □현장카드결제             □기타</t>
         </is>
       </c>
       <c r="I27" s="72" t="n"/>
     </row>
     <row r="28" s="88">
-      <c r="A28" s="71" t="inlineStr">
-        <is>
-          <t>■결제방법을 체크해 주세요.</t>
+      <c r="A28" s="72" t="inlineStr">
+        <is>
+          <t>■영수증발행 방법을 체크해주세요.    (법인기업은 간이영수증을 사용 할 수 없습니다.)</t>
         </is>
       </c>
       <c r="I28" s="72" t="n"/>
@@ -2262,67 +2216,79 @@
     <row r="29" s="88">
       <c r="A29" s="72" t="inlineStr">
         <is>
-          <t>□은행송금             □현장현금결제             □현장카드결제             □기타</t>
+          <t>■세금계산서 발행             □거래명세표 발행           □입금표 발행           □기타</t>
         </is>
       </c>
       <c r="I29" s="72" t="n"/>
     </row>
     <row r="30" s="88">
-      <c r="A30" s="72" t="inlineStr">
-        <is>
-          <t>■영수증발행 방법을 체크해주세요.    (법인기업은 간이영수증을 사용 할 수 없습니다.)</t>
-        </is>
-      </c>
-      <c r="I30" s="72" t="n"/>
-    </row>
-    <row r="31" s="88">
-      <c r="A31" s="72" t="inlineStr">
-        <is>
-          <t>■세금계산서 발행             □거래명세표 발행           □입금표 발행           □기타</t>
-        </is>
-      </c>
-      <c r="I31" s="72" t="n"/>
+      <c r="A30" s="73" t="inlineStr">
+        <is>
+          <t>세금계산서 발행시 사업등록증 사본에 받으실 이메일 주소와 담당자명, 연락처를 기재하시어 FAX로 넣어주세요.</t>
+        </is>
+      </c>
+      <c r="I30" s="73" t="n"/>
+    </row>
+    <row r="31" ht="18" customHeight="1" s="88">
+      <c r="A31" s="74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">◆비품 신청시 유의 사항◆ </t>
+        </is>
+      </c>
+      <c r="I31" s="87" t="n"/>
+      <c r="J31" s="87" t="n"/>
+      <c r="K31" s="87" t="n"/>
+      <c r="L31" s="87" t="n"/>
+      <c r="M31" s="87" t="n"/>
+      <c r="N31" s="87" t="n"/>
+      <c r="O31" s="87" t="n"/>
+      <c r="P31" s="87" t="n"/>
     </row>
     <row r="32" s="88">
-      <c r="A32" s="73" t="inlineStr">
-        <is>
-          <t>세금계산서 발행시 사업등록증 사본에 받으실 이메일 주소와 담당자명, 연락처를 기재하시어 FAX로 넣어주세요.</t>
-        </is>
-      </c>
-      <c r="I32" s="73" t="n"/>
-    </row>
-    <row r="33" ht="18" customHeight="1" s="88">
-      <c r="A33" s="74" t="inlineStr">
-        <is>
-          <t xml:space="preserve">◆비품 신청시 유의 사항◆ </t>
-        </is>
-      </c>
-      <c r="I33" s="87" t="n"/>
-      <c r="J33" s="87" t="n"/>
-      <c r="K33" s="87" t="n"/>
-      <c r="L33" s="87" t="n"/>
-      <c r="M33" s="87" t="n"/>
-      <c r="N33" s="87" t="n"/>
-      <c r="O33" s="87" t="n"/>
-      <c r="P33" s="87" t="n"/>
+      <c r="A32" s="72" t="inlineStr">
+        <is>
+          <t>①상기 금액은 전시기간내의 (1~4일) 금액이며 부가세는 별도입니다.</t>
+        </is>
+      </c>
+      <c r="I32" s="72" t="n"/>
+      <c r="J32" s="52" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> □ 위의 개인정보 수집에 대해 동의합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" s="88">
+      <c r="A33" s="72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">②임차료는 전시 시작 전 완납되어야만 주문서의 효력이 발행됩니다. </t>
+        </is>
+      </c>
+      <c r="I33" s="72" t="n"/>
+      <c r="J33" s="72" t="n"/>
+      <c r="K33" s="72" t="n"/>
+      <c r="L33" s="72" t="n"/>
+      <c r="M33" s="72" t="n"/>
+      <c r="N33" s="72" t="n"/>
+      <c r="O33" s="72" t="n"/>
+      <c r="P33" s="72" t="n"/>
     </row>
     <row r="34" s="88">
       <c r="A34" s="72" t="inlineStr">
         <is>
-          <t>①상기 금액은 전시기간내의 (1~4일) 금액이며 부가세는 별도입니다.</t>
+          <t>③상품이 출고된 상태에서 취소시 환불은 불가합니다.</t>
         </is>
       </c>
       <c r="I34" s="72" t="n"/>
       <c r="J34" s="52" t="inlineStr">
         <is>
-          <t xml:space="preserve"> □ 위의 개인정보 수집에 대해 동의합니다.</t>
+          <t>년      월     일</t>
         </is>
       </c>
     </row>
     <row r="35" s="88">
       <c r="A35" s="72" t="inlineStr">
         <is>
-          <t xml:space="preserve">②임차료는 전시 시작 전 완납되어야만 주문서의 효력이 발행됩니다. </t>
+          <t>④대여 물품의 분실,파손시 구매금액의 85% 금액을 추가 배상하셔야합니다.</t>
         </is>
       </c>
       <c r="I35" s="72" t="n"/>
@@ -2334,118 +2300,87 @@
       <c r="O35" s="72" t="n"/>
       <c r="P35" s="72" t="n"/>
     </row>
-    <row r="36" s="88">
+    <row r="36" ht="15.75" customHeight="1" s="88">
       <c r="A36" s="72" t="inlineStr">
         <is>
-          <t>③상품이 출고된 상태에서 취소시 환불은 불가합니다.</t>
+          <t>⑤은행 송금시 송금자명을 "업체명"으로 해주시고 개인일 경우 반드시 송금자명을 기재하여주세요.</t>
         </is>
       </c>
       <c r="I36" s="72" t="n"/>
-      <c r="J36" s="52" t="inlineStr">
-        <is>
-          <t>년      월     일</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" s="88">
-      <c r="A37" s="72" t="inlineStr">
-        <is>
-          <t>④대여 물품의 분실,파손시 구매금액의 85% 금액을 추가 배상하셔야합니다.</t>
-        </is>
-      </c>
-      <c r="I37" s="72" t="n"/>
-      <c r="J37" s="72" t="n"/>
-      <c r="K37" s="72" t="n"/>
-      <c r="L37" s="72" t="n"/>
-      <c r="M37" s="72" t="n"/>
-      <c r="N37" s="72" t="n"/>
-      <c r="O37" s="72" t="n"/>
-      <c r="P37" s="72" t="n"/>
-    </row>
-    <row r="38" ht="15.75" customHeight="1" s="88">
-      <c r="A38" s="72" t="inlineStr">
-        <is>
-          <t>⑤은행 송금시 송금자명을 "업체명"으로 해주시고 개인일 경우 반드시 송금자명을 기재하여주세요.</t>
-        </is>
-      </c>
-      <c r="I38" s="72" t="n"/>
-      <c r="J38" s="72" t="n"/>
-      <c r="K38" s="72" t="n"/>
-      <c r="L38" s="72" t="n"/>
-      <c r="M38" s="72" t="n"/>
-      <c r="N38" s="39" t="inlineStr">
+      <c r="J36" s="72" t="n"/>
+      <c r="K36" s="72" t="n"/>
+      <c r="L36" s="72" t="n"/>
+      <c r="M36" s="72" t="n"/>
+      <c r="N36" s="39" t="inlineStr">
         <is>
           <t xml:space="preserve">제공자 : </t>
         </is>
       </c>
-      <c r="O38" s="72" t="n"/>
-      <c r="P38" s="72" t="inlineStr">
+      <c r="O36" s="72" t="n"/>
+      <c r="P36" s="72" t="inlineStr">
         <is>
           <t>(서명)</t>
         </is>
       </c>
     </row>
-    <row r="39" ht="24" customHeight="1" s="88">
-      <c r="A39" s="68" t="inlineStr">
+    <row r="37" ht="24" customHeight="1" s="88">
+      <c r="A37" s="68" t="inlineStr">
         <is>
           <t>문의사항은 홈페이지  http://www.kdrental.com 참고하시기 바랍니다.</t>
         </is>
       </c>
-      <c r="I39" s="38" t="n"/>
-      <c r="J39" s="38" t="n"/>
-      <c r="K39" s="38" t="n"/>
-      <c r="L39" s="38" t="n"/>
-      <c r="M39" s="38" t="n"/>
-      <c r="N39" s="38" t="n"/>
-      <c r="O39" s="38" t="n"/>
-      <c r="P39" s="38" t="n"/>
-    </row>
-    <row r="40" s="88">
-      <c r="A40" s="52" t="inlineStr">
+      <c r="I37" s="38" t="n"/>
+      <c r="J37" s="38" t="n"/>
+      <c r="K37" s="38" t="n"/>
+      <c r="L37" s="38" t="n"/>
+      <c r="M37" s="38" t="n"/>
+      <c r="N37" s="38" t="n"/>
+      <c r="O37" s="38" t="n"/>
+      <c r="P37" s="38" t="n"/>
+    </row>
+    <row r="38" s="88">
+      <c r="A38" s="52" t="inlineStr">
         <is>
           <t>[ ㈜케이디알에스 I Tel : 02-907-9270 I Fax : 02-907-9272 I e-maill : kdrs@kdrental.com  ]</t>
         </is>
       </c>
-      <c r="I40" s="76" t="inlineStr">
+      <c r="I38" s="76" t="inlineStr">
         <is>
           <t>㈜케이디알에스</t>
         </is>
       </c>
     </row>
+    <row r="39" s="88"/>
+    <row r="40" s="88"/>
     <row r="41" s="88"/>
-    <row r="42" s="88"/>
-    <row r="43" s="88"/>
   </sheetData>
-  <mergeCells count="60">
+  <mergeCells count="58">
+    <mergeCell ref="A25:C25"/>
     <mergeCell ref="B16:C16"/>
     <mergeCell ref="A30:H30"/>
-    <mergeCell ref="A39:H39"/>
-    <mergeCell ref="A24:E24"/>
     <mergeCell ref="G2:H2"/>
-    <mergeCell ref="F25:G25"/>
-    <mergeCell ref="G27:H27"/>
-    <mergeCell ref="A27:C27"/>
-    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="A24:H24"/>
     <mergeCell ref="A36:H36"/>
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="B18:C18"/>
     <mergeCell ref="A6:B6"/>
     <mergeCell ref="B12:C12"/>
     <mergeCell ref="C2:E2"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="F24:G24"/>
+    <mergeCell ref="F21:G21"/>
     <mergeCell ref="A7:H7"/>
     <mergeCell ref="B11:C11"/>
-    <mergeCell ref="A25:E25"/>
     <mergeCell ref="B14:C14"/>
     <mergeCell ref="G6:H6"/>
     <mergeCell ref="I1:Q1"/>
     <mergeCell ref="B17:C17"/>
     <mergeCell ref="A37:H37"/>
+    <mergeCell ref="A27:H27"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="G3:H3"/>
     <mergeCell ref="B8:C8"/>
     <mergeCell ref="B13:C13"/>
+    <mergeCell ref="A21:E21"/>
+    <mergeCell ref="I38:Q38"/>
     <mergeCell ref="A26:H26"/>
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="B19:C19"/>
@@ -2454,13 +2389,13 @@
     <mergeCell ref="G5:H5"/>
     <mergeCell ref="F23:G23"/>
     <mergeCell ref="C3:E3"/>
-    <mergeCell ref="E27:F27"/>
+    <mergeCell ref="F22:G22"/>
+    <mergeCell ref="A23:E23"/>
+    <mergeCell ref="A33:H33"/>
     <mergeCell ref="J34:P34"/>
-    <mergeCell ref="A33:H33"/>
-    <mergeCell ref="A23:E23"/>
     <mergeCell ref="B9:C9"/>
     <mergeCell ref="A32:H32"/>
-    <mergeCell ref="I40:Q40"/>
+    <mergeCell ref="A22:E22"/>
     <mergeCell ref="C6:E6"/>
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="G4:H4"/>
@@ -2468,15 +2403,16 @@
     <mergeCell ref="A35:H35"/>
     <mergeCell ref="A29:H29"/>
     <mergeCell ref="C5:E5"/>
-    <mergeCell ref="A34:H34"/>
-    <mergeCell ref="J36:P36"/>
+    <mergeCell ref="E25:F25"/>
+    <mergeCell ref="A38:H38"/>
     <mergeCell ref="B20:C20"/>
-    <mergeCell ref="A38:H38"/>
+    <mergeCell ref="G25:H25"/>
     <mergeCell ref="A28:H28"/>
     <mergeCell ref="C4:E4"/>
-    <mergeCell ref="J3:P32"/>
+    <mergeCell ref="J3:P30"/>
     <mergeCell ref="A31:H31"/>
-    <mergeCell ref="A40:H40"/>
+    <mergeCell ref="J32:P32"/>
+    <mergeCell ref="A34:H34"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0" right="0" top="0.7480314960629921" bottom="0" header="0.3149606299212598" footer="0.3149606299212598"/>
